--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>122708338</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -802,45 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133059568</v>
+        <v>133059563</v>
       </c>
       <c r="B3" t="n">
-        <v>101348</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483221</v>
+        <v>483242</v>
       </c>
       <c r="R3" t="n">
-        <v>6991568</v>
+        <v>6991402</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -872,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,52 +908,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133059560</v>
+        <v>133059573</v>
       </c>
       <c r="B4" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483344</v>
+        <v>483225</v>
       </c>
       <c r="R4" t="n">
-        <v>6991330</v>
+        <v>6991633</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 bål</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,48 +1015,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133059570</v>
+        <v>133059560</v>
       </c>
       <c r="B5" t="n">
-        <v>101348</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483224</v>
+        <v>483344</v>
       </c>
       <c r="R5" t="n">
-        <v>6991630</v>
+        <v>6991330</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1099,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133059565</v>
+        <v>133059574</v>
       </c>
       <c r="B6" t="n">
-        <v>101348</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483196</v>
+        <v>483226</v>
       </c>
       <c r="R6" t="n">
-        <v>6991546</v>
+        <v>6991635</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1241,7 @@
         <v>133059569</v>
       </c>
       <c r="B7" t="n">
-        <v>104652</v>
+        <v>104707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,51 +1345,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133059563</v>
+        <v>133059565</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>101403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483242</v>
+        <v>483196</v>
       </c>
       <c r="R8" t="n">
-        <v>6991402</v>
+        <v>6991546</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1425,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,7 +1434,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1460,7 +1455,7 @@
         <v>133059566</v>
       </c>
       <c r="B9" t="n">
-        <v>101348</v>
+        <v>101403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,6 +1556,220 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133059568</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483221</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991568</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133059570</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483224</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991630</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20450-2026 artfynd.xlsx
+++ b/artfynd/A 20450-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122708338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059563</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059560</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059569</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059565</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059568</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,8 +1820,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059570</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>